--- a/GourmetProject/outputs/019ff002-169f-7f63-b9c7-3756bc04c1b9/event.xlsx
+++ b/GourmetProject/outputs/019ff002-169f-7f63-b9c7-3756bc04c1b9/event.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="Rdccd1303eef846db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="Re612b83caa4f4021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="R8a547c5be26c4e0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="R7845934732ef4d03"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1414,7 +1414,7 @@
       </x:c>
       <x:c r="D9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每满 {threshold} 金币获得 {goldPer}金币，最高 {maxGain}金币</x:t>
+          <x:t xml:space="preserve">每满 [gold]{threshold} 金币[/gold]获得 [gold]{goldPer}金币[/gold]，最高 [gold]{maxGain}金币[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </x:c>
       <x:c r="J9" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">金币 +{gain}</x:t>
+          <x:t xml:space="preserve">[gold]金币 +{gain}[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="K9" t="n">
@@ -1455,7 +1455,7 @@
       </x:c>
       <x:c r="D10" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">一个华丽的机器，投入金币有概率获得任何奖励</x:t>
+          <x:t xml:space="preserve">一个华丽的机器，投入[gold]金币[/gold]有概率获得任何奖励</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr">
@@ -1592,33 +1592,35 @@
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>最后一灶也会发光</x:v>
-      </x:c>
-      <x:c r="D14" t="str">
-        <x:v>阳泉酒家收档前又来了一桌客人。小当家把最后一眼灶火让给你：“用哪道料理招待他们？”</x:v>
-      </x:c>
-      <x:c r="E14" t="str">
-        <x:v>Event|Reward</x:v>
-      </x:c>
-      <x:c r="F14"/>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最后一灶也会发光</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">阳泉酒家收档前又来了一桌客人。小当家把最后一眼灶火让给你：“用哪道料理招待他们？”</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Event|Reward</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14"/>
-      <x:c r="J14"/>
       <x:c r="K14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14"/>
-      <x:c r="M14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2250,7 +2252,7 @@
       </x:c>
       <x:c r="F13" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">经平台核实，对方的言论不实，特此赠予餐厅一件装饰品，以表安慰</x:t>
+          <x:t xml:space="preserve">经平台核实，对方的言论不实，特此赠予餐厅一件[term]装饰品[/term]，以表安慰</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
@@ -2258,9 +2260,9 @@
           <x:t xml:space="preserve">minGold:30</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">需要至少 30 金币</x:t>
+      <x:c r="H13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要至少 [gold]30 金币[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="I13" s="1" t="inlineStr">
@@ -2309,7 +2311,7 @@
           <x:t xml:space="preserve">hasRecipeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="2" t="inlineStr">
+      <x:c r="H14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">需要食谱中至少有 1 个食物</x:t>
         </x:is>
@@ -2388,7 +2390,7 @@
       </x:c>
       <x:c r="E16" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">金币 +{gain}</x:t>
+          <x:t xml:space="preserve">[gold]金币 +{gain}[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="I16" s="1" t="inlineStr">
@@ -2547,12 +2549,12 @@
       </x:c>
       <x:c r="E20" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">心情大好，下次营业获得的金币额外+60%</x:t>
+          <x:t xml:space="preserve">心情大好，下次营业获得的[gold]金币[/gold]额外[gold]+60%[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">下一次营业基础金币 ×1.6。</x:t>
+          <x:t xml:space="preserve">下一次营业基础[gold]金币[/gold] ×1.6。</x:t>
         </x:is>
       </x:c>
       <x:c r="I20" s="1" t="inlineStr">
@@ -2593,12 +2595,12 @@
       </x:c>
       <x:c r="E21" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所有食物分数+2！这就是知识的力量</x:t>
+          <x:t xml:space="preserve">[context]所有[/context]食物[strong]分数[/strong][score]+2[/score]！这就是知识的力量</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数 +2。</x:t>
+          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久[strong]分数[/strong] [score]+2[/score]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I21" s="1" t="inlineStr">
@@ -2639,12 +2641,12 @@
       </x:c>
       <x:c r="E22" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本周后续营业的金币奖励提升30%</x:t>
+          <x:t xml:space="preserve">本周后续营业的[gold]金币[/gold]奖励提升[gold]30%[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本周后续营业基础金币 ×1.3。</x:t>
+          <x:t xml:space="preserve">本周后续营业基础[gold]金币[/gold] ×1.3。</x:t>
         </x:is>
       </x:c>
       <x:c r="I22" s="1" t="inlineStr">
@@ -2685,7 +2687,7 @@
       </x:c>
       <x:c r="E23" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得两个调味相关的消耗品</x:t>
+          <x:t xml:space="preserve">获得两个调味相关的[term]消耗品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="1" t="inlineStr">
@@ -2731,12 +2733,12 @@
       </x:c>
       <x:c r="E24" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">星级评鉴美味值要求提升20%，金币奖励翻倍</x:t>
+          <x:t xml:space="preserve">[context]星级评鉴[/context]美味值要求提升20%，[gold]金币[/gold]奖励翻倍</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">后续星级评鉴目标 ×1.2，基础金币 ×2。</x:t>
+          <x:t xml:space="preserve">后续[context]星级评鉴[/context]目标 ×1.2，基础[gold]金币[/gold] ×2。</x:t>
         </x:is>
       </x:c>
       <x:c r="I24" s="1" t="inlineStr">
@@ -2930,12 +2932,12 @@
       </x:c>
       <x:c r="E29" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得1个装饰品</x:t>
+          <x:t xml:space="preserve">获得1个[term]装饰品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">支付 30 金币，随机获得 1 个非诅咒装饰品。</x:t>
+          <x:t xml:space="preserve">支付 [gold]30 金币[/gold]，随机获得 1 个非诅咒[term]装饰品[/term]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I29" s="1" t="inlineStr">
@@ -2991,12 +2993,12 @@
       </x:c>
       <x:c r="E31" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得100金币和1个负面装饰品</x:t>
+          <x:t xml:space="preserve">获得[gold]100金币[/gold]和1个负面[term]装饰品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得 100 金币和 1 个诅咒装饰品。</x:t>
+          <x:t xml:space="preserve">获得 [gold]100 金币[/gold]和 1 个诅咒[term]装饰品[/term]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I31" s="1" t="inlineStr">
@@ -3052,12 +3054,12 @@
       </x:c>
       <x:c r="E33" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">下次营业金币-40%</x:t>
+          <x:t xml:space="preserve">下次营业[gold]金币-40%[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得 100 金币和 1 个随机消耗品；下一次营业基础金币 ×0.6。</x:t>
+          <x:t xml:space="preserve">获得 [gold]100 金币[/gold]和 1 个随机[term]消耗品[/term]；下一次营业基础[gold]金币[/gold] ×0.6。</x:t>
         </x:is>
       </x:c>
       <x:c r="I33" s="1" t="inlineStr">
@@ -3364,7 +3366,7 @@
       </x:c>
       <x:c r="F40" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个装饰品给你</x:t>
+          <x:t xml:space="preserve">顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个[term]装饰品[/term]给你</x:t>
         </x:is>
       </x:c>
       <x:c r="I40" s="1" t="inlineStr">
@@ -3405,7 +3407,7 @@
       </x:c>
       <x:c r="E41" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得两个调整单类的消耗品</x:t>
+          <x:t xml:space="preserve">获得两个调整单类的[term]消耗品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="1" t="inlineStr">
@@ -3451,12 +3453,12 @@
       </x:c>
       <x:c r="E42" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得一个装饰品</x:t>
+          <x:t xml:space="preserve">获得一个[term]装饰品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">随机获得 1 个非诅咒装饰品。</x:t>
+          <x:t xml:space="preserve">随机获得 1 个非诅咒[term]装饰品[/term]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I42" s="1" t="inlineStr">
@@ -3579,12 +3581,12 @@
       </x:c>
       <x:c r="E45" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">参与奖：金币+50</x:t>
+          <x:t xml:space="preserve">参与奖：[gold]金币+50[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得 50 金币。</x:t>
+          <x:t xml:space="preserve">获得 [gold]50 金币[/gold]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I45" s="1" t="inlineStr">
@@ -3625,7 +3627,7 @@
       </x:c>
       <x:c r="E46" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去抢救，金币-20</x:t>
+          <x:t xml:space="preserve">去抢救，[gold]金币-20[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="1" t="inlineStr">
@@ -3652,7 +3654,7 @@
       <x:c r="M46" s="2" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N46" s="2" t="inlineStr">
+      <x:c r="N46" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">白色蘑菇刚入口，舌尖便开始发麻，眼前的餐厅转了起来。</x:t>
         </x:is>
@@ -3703,7 +3705,7 @@
       <x:c r="M47" s="2" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N47" s="2" t="inlineStr">
+      <x:c r="N47" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">白色蘑菇清甜鲜嫩，吃完后身体毫无异样。</x:t>
         </x:is>
@@ -3727,12 +3729,12 @@
       </x:c>
       <x:c r="E48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">见好就收，领取 70 金币</x:t>
+          <x:t xml:space="preserve">见好就收，领取 [gold]70 金币[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">你把剩下的白色蘑菇卖给了识货的客人，获得 70 金币。</x:t>
+          <x:t xml:space="preserve">你把剩下的白色蘑菇卖给了识货的客人，获得 [gold]70 金币[/gold]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I48" s="1" t="inlineStr">
@@ -3819,7 +3821,7 @@
       </x:c>
       <x:c r="E50" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去抢救，金币-40</x:t>
+          <x:t xml:space="preserve">去抢救，[gold]金币-40[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="1" t="inlineStr">
@@ -3846,7 +3848,7 @@
       <x:c r="M50" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N50" s="2" t="inlineStr">
+      <x:c r="N50" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">红色蘑菇辛辣得反常，没过多久，你的视线便开始模糊。</x:t>
         </x:is>
@@ -3897,7 +3899,7 @@
       <x:c r="M51" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N51" s="2" t="inlineStr">
+      <x:c r="N51" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">红色蘑菇入口微辣，却没有任何毒性，你又安全过了一关。</x:t>
         </x:is>
@@ -3921,12 +3923,12 @@
       </x:c>
       <x:c r="E52" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">稳妥收手，领取 120 金币</x:t>
+          <x:t xml:space="preserve">稳妥收手，领取 [gold]120 金币[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">你把剩余蘑菇高价转让，获得 120 金币。</x:t>
+          <x:t xml:space="preserve">你把剩余蘑菇高价转让，获得 [gold]120 金币[/gold]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I52" s="1" t="inlineStr">
@@ -4013,7 +4015,7 @@
       </x:c>
       <x:c r="E54" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去icu抢救，金币-60</x:t>
+          <x:t xml:space="preserve">去icu抢救，[gold]金币-60[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="1" t="inlineStr">
@@ -4040,7 +4042,7 @@
       <x:c r="M54" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N54" s="2" t="inlineStr">
+      <x:c r="N54" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">绿色蘑菇鲜得惊人——紧接着，房间里的所有东西都变成了绿色。</x:t>
         </x:is>
@@ -4064,12 +4066,12 @@
       </x:c>
       <x:c r="E55" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">大获成功！获得传奇装饰品</x:t>
+          <x:t xml:space="preserve">大获成功！获得传奇[term]装饰品[/term]</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">你完整记住了三种蘑菇的风味，并获得 1 个传奇装饰品。</x:t>
+          <x:t xml:space="preserve">你完整记住了三种蘑菇的风味，并获得 1 个传奇[term]装饰品[/term]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I55" s="1" t="inlineStr">
@@ -4091,7 +4093,7 @@
       <x:c r="M55" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N55" s="2" t="inlineStr">
+      <x:c r="N55" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">绿色蘑菇化成一股清香。你连过三关，主厨惊讶地捧出了珍藏礼物。</x:t>
         </x:is>
@@ -4156,12 +4158,12 @@
       </x:c>
       <x:c r="E57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">下次营业金币+60%</x:t>
+          <x:t xml:space="preserve">下次营业[gold]金币+60%[/gold]</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">众厨师如约来访。下一次营业获得的基础金币提高60%。</x:t>
+          <x:t xml:space="preserve">众厨师如约来访。下一次营业获得的基础[gold]金币[/gold]提高[gold]60%[/gold]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I57" s="1" t="inlineStr">
@@ -4243,12 +4245,12 @@
       </x:c>
       <x:c r="E59" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">收下定金</x:t>
+          <x:t xml:space="preserve">金币+100</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">获得100金币。</x:t>
+          <x:t xml:space="preserve">获得[gold]100金币[/gold]。</x:t>
         </x:is>
       </x:c>
       <x:c r="I59" s="1" t="inlineStr">
@@ -4330,26 +4332,22 @@
       </x:c>
       <x:c r="E61" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">收下两道回礼</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从众人的回礼中获得2个随机风味食物。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
-        </x:is>
+          <x:t xml:space="preserve">获得两个食物3选1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F61" s="1" t="str">
+        <x:v>十二位厨师依次端上拿手菜。你从两组三道回礼中各选一道，加入食谱。</x:v>
+      </x:c>
+      <x:c r="G61"/>
+      <x:c r="H61"/>
+      <x:c r="I61" s="1" t="str">
+        <x:v>EnqueueDishChoice</x:v>
       </x:c>
       <x:c r="J61" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flavored_dish_2|众人的回礼</x:t>
-        </x:is>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K61" s="1" t="str">
+        <x:v>dish_choice_3|第一道回礼</x:v>
       </x:c>
       <x:c r="L61" s="1" t="n">
         <x:v>1</x:v>
@@ -4359,465 +4357,600 @@
       </x:c>
     </x:row>
     <x:row r="62">
-      <x:c r="B62" s="1" t="inlineStr">
+      <x:c r="A62"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62" s="1" t="str">
+        <x:v>EnqueueDishChoice</x:v>
+      </x:c>
+      <x:c r="J62" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K62" s="1" t="str">
+        <x:v>dish_choice_3|第二道回礼</x:v>
+      </x:c>
+      <x:c r="L62" s="1"/>
+      <x:c r="M62" s="2"/>
+      <x:c r="N62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" s="1" t="inlineStr">
+      <x:c r="C63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E62" s="1" t="inlineStr">
+      <x:c r="D63" s="2"/>
+      <x:c r="E63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">喝黑咖啡</x:t>
         </x:is>
       </x:c>
-      <x:c r="F62" s="1" t="inlineStr">
+      <x:c r="F63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">咖啡苦得恰到好处，你一下清醒过来，连夜整理了下一次营业安排。</x:t>
         </x:is>
       </x:c>
-      <x:c r="I62" s="1" t="inlineStr">
+      <x:c r="G63"/>
+      <x:c r="H63"/>
+      <x:c r="I63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J62" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K62" s="1" t="inlineStr">
+      <x:c r="J63" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="L62" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M62" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63">
-      <x:c r="B63" s="1" t="inlineStr">
+      <x:c r="L63" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M63" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N63"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64"/>
+      <x:c r="B64" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_coffee_reward</x:t>
         </x:is>
       </x:c>
-      <x:c r="C63" s="1" t="inlineStr">
+      <x:c r="C64" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="D63" s="2" t="inlineStr">
+      <x:c r="D64" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
         </x:is>
       </x:c>
-      <x:c r="E63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下两次营业金币+60%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下两次营业基础金币×1.6。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I63" s="1" t="str">
-        <x:v>AddBusinessGoldPct</x:v>
-      </x:c>
-      <x:c r="J63" s="1" t="n">
+      <x:c r="E64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下两次营业[gold]金币+60%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下两次营业基础[gold]金币[/gold]×1.6。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64"/>
+      <x:c r="H64"/>
+      <x:c r="I64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J64" s="1" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="K63" s="1" t="str">
-        <x:v>Next:2</x:v>
-      </x:c>
-      <x:c r="L63" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M63" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64">
-      <x:c r="B64" s="1" t="inlineStr">
+      <x:c r="K64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Next:2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L64" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M64" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N64"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65"/>
+      <x:c r="B65" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
         </x:is>
       </x:c>
-      <x:c r="C64" s="1" t="inlineStr">
+      <x:c r="C65" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E64" s="1" t="inlineStr">
+      <x:c r="D65" s="2"/>
+      <x:c r="E65" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">点樱桃派</x:t>
         </x:is>
       </x:c>
-      <x:c r="F64" s="1" t="inlineStr">
+      <x:c r="F65" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">樱桃派美味可口，一天的疲惫一扫而空</x:t>
         </x:is>
-      </x:c>
-      <x:c r="I64" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J64" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K64" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L64" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M64" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65">
-      <x:c r="B65" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_pie_reward</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C65" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D65" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E65" s="1" t="str">
-        <x:v>恢复1颗红心</x:v>
-      </x:c>
-      <x:c r="F65" t="str">
-        <x:v>恢复1颗红心，不超过红心上限。</x:v>
       </x:c>
       <x:c r="G65"/>
       <x:c r="H65"/>
-      <x:c r="I65" s="1" t="str">
-        <x:v>RestoreHearts</x:v>
+      <x:c r="I65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
       </x:c>
       <x:c r="J65" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K65" s="1" t="str">
-        <x:v>-</x:v>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
       </x:c>
       <x:c r="L65" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M65" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N65"/>
     </x:row>
     <x:row r="66">
+      <x:c r="A66"/>
       <x:c r="B66" s="1" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_pie_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心，不超过红心上限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66"/>
+      <x:c r="H66"/>
+      <x:c r="I66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RestoreHearts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J66" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L66" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M66" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N66"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67"/>
+      <x:c r="B67" s="1" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
         </x:is>
       </x:c>
-      <x:c r="C66" s="1" t="inlineStr">
+      <x:c r="C67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="1" t="inlineStr">
+      <x:c r="D67" s="2"/>
+      <x:c r="E67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">听听木头怎么说</x:t>
         </x:is>
       </x:c>
-      <x:c r="F66" s="1" t="inlineStr">
+      <x:c r="F67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">木头女士转述了一段古怪配方。你回去试了一夜，食谱里原有的菜竟都变得更好吃了。</x:t>
         </x:is>
       </x:c>
-      <x:c r="I66" s="1" t="inlineStr">
+      <x:c r="G67"/>
+      <x:c r="H67"/>
+      <x:c r="I67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J66" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="1" t="inlineStr">
+      <x:c r="J67" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="L66" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M66" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67">
-      <x:c r="B67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_log_reward</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D67" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">所有食物分数永久+10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数+10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J67" s="1" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
       <x:c r="L67" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M67" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N67"/>
     </x:row>
     <x:row r="68">
       <x:c r="A68"/>
-      <x:c r="B68" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice</x:v>
-      </x:c>
-      <x:c r="C68" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D68"/>
-      <x:c r="E68" t="str">
-        <x:v>颠一锅黄金炒饭</x:v>
-      </x:c>
-      <x:c r="F68" t="str">
-        <x:v>蛋液裹住每一粒米，揭盖时金光一闪。旅人把碗吃得干干净净，还在桌上留下赏钱。</x:v>
+      <x:c r="B68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_log_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="1" t="str">
+        <x:v>[context]所有[/context]食物[strong]分数[/strong]永久[score]+15[/score]</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久[strong]分数[/strong][score]+15[/score]</x:t>
+        </x:is>
       </x:c>
       <x:c r="G68"/>
       <x:c r="H68"/>
-      <x:c r="I68" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J68" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K68" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L68" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M68" t="n">
+      <x:c r="I68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J68" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L68" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M68" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N68"/>
     </x:row>
     <x:row r="69">
       <x:c r="A69"/>
-      <x:c r="B69" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice_reward</x:v>
-      </x:c>
-      <x:c r="C69" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D69" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice</x:v>
-      </x:c>
-      <x:c r="E69" t="str">
-        <x:v>收下80金币赏钱</x:v>
-      </x:c>
-      <x:c r="F69" t="str">
-        <x:v>旅人因黄金炒饭心满意足，留下80金币。</x:v>
+      <x:c r="B69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="2"/>
+      <x:c r="E69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">黄金炒饭</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">蛋液裹住每一粒米，揭盖时金光一闪。旅人把碗吃得干干净净，还在桌上留下赏钱。</x:t>
+        </x:is>
       </x:c>
       <x:c r="G69"/>
       <x:c r="H69"/>
-      <x:c r="I69" t="str">
-        <x:v>GainGold</x:v>
-      </x:c>
-      <x:c r="J69" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="K69" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L69" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M69" t="n">
+      <x:c r="I69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J69" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L69" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M69" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N69"/>
     </x:row>
     <x:row r="70">
       <x:c r="A70"/>
-      <x:c r="B70" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu</x:v>
-      </x:c>
-      <x:c r="C70" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D70"/>
-      <x:c r="E70" t="str">
-        <x:v>补齐麻婆豆腐的第六味</x:v>
-      </x:c>
-      <x:c r="F70" t="str">
-        <x:v>你把大豆炒得酥香，让麻、辣、香、色、烫之外又添一层爽脆。小当家笑着点了点头。</x:v>
+      <x:c r="B70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">收下[gold]80金币[/gold]赏钱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">旅人因黄金炒饭心满意足，留下[gold]80金币[/gold]。</x:t>
+        </x:is>
       </x:c>
       <x:c r="G70"/>
       <x:c r="H70"/>
-      <x:c r="I70" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M70" t="n">
+      <x:c r="I70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GainGold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J70" s="1" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L70" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M70" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N70"/>
     </x:row>
     <x:row r="71">
       <x:c r="A71"/>
-      <x:c r="B71" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu_reward</x:v>
-      </x:c>
-      <x:c r="C71" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D71" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu</x:v>
-      </x:c>
-      <x:c r="E71" t="str">
-        <x:v>给1个食物添加随机风味</x:v>
-      </x:c>
-      <x:c r="F71" t="str">
-        <x:v>从“酥”的灵感中举一反三，为食谱中1个食物添加随机风味。</x:v>
+      <x:c r="B71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">麻婆豆腐</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你把大豆炒得酥香，让麻、辣、香、色、烫之外又添一层爽脆。小当家笑着点了点头。</x:t>
+        </x:is>
       </x:c>
       <x:c r="G71"/>
       <x:c r="H71"/>
-      <x:c r="I71" t="str">
-        <x:v>AddRandomRecipeFlavor</x:v>
-      </x:c>
-      <x:c r="J71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K71" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M71" t="n">
+      <x:c r="I71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J71" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L71" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M71" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N71"/>
     </x:row>
     <x:row r="72">
       <x:c r="A72"/>
-      <x:c r="B72" t="str">
-        <x:v>opt_chuka_ichiban_dumpling</x:v>
-      </x:c>
-      <x:c r="C72" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D72"/>
-      <x:c r="E72" t="str">
-        <x:v>蒸一笼大宇宙烧卖</x:v>
-      </x:c>
-      <x:c r="F72" t="str">
-        <x:v>一只烧卖占满了蒸笼，切开正好够全店分。众人围桌大笑，收档前的疲惫一扫而空。</x:v>
+      <x:c r="B72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得2个风味强化箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你从“酥”的灵感中举一反三，从六种风味强化箱中随机获得2个，可能重复。</x:t>
+        </x:is>
       </x:c>
       <x:c r="G72"/>
       <x:c r="H72"/>
-      <x:c r="I72" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M72" t="n">
+      <x:c r="I72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J72" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ids:item_active_season_sweet,item_active_season_bitter,item_active_season_umami,item_active_season_numb,item_active_season_sour,item_active_season_salty|Replace</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L72" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M72" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N72"/>
     </x:row>
     <x:row r="73">
       <x:c r="A73"/>
-      <x:c r="B73" t="str">
-        <x:v>opt_chuka_ichiban_dumpling_reward</x:v>
-      </x:c>
-      <x:c r="C73" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D73" t="str">
-        <x:v>opt_chuka_ichiban_dumpling</x:v>
-      </x:c>
-      <x:c r="E73" t="str">
-        <x:v>恢复1颗红心</x:v>
-      </x:c>
-      <x:c r="F73" t="str">
-        <x:v>大家分享烧卖后重新打起精神。恢复1颗红心，不超过红心上限。</x:v>
+      <x:c r="B73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="2"/>
+      <x:c r="E73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大宇宙烧卖</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一只烧卖占满了蒸笼，切开正好够全店分。众人围桌大笑，收档前的疲惫一扫而空。</x:t>
+        </x:is>
       </x:c>
       <x:c r="G73"/>
       <x:c r="H73"/>
-      <x:c r="I73" t="str">
-        <x:v>RestoreHearts</x:v>
-      </x:c>
-      <x:c r="J73" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K73" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L73" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M73" t="n">
+      <x:c r="I73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J73" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L73" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M73" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74"/>
+      <x:c r="B74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大家分享烧卖后重新打起精神。恢复1颗红心，不超过红心上限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RestoreHearts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N74"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
